--- a/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
@@ -771,6 +771,9 @@
       <c r="C41" t="str">
         <v>616_康乃馨紫精灵_Purple Elves_undefined_20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -829,7 +832,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0310108610197778158303030205558515510555556451055550</v>
+        <v>0310108610197778158303030205558515510555556451055555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -775,9 +775,87 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>5</v>
+      </c>
+      <c r="C43" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>699_火焰兰果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>6</v>
+      </c>
+      <c r="C50" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -832,7 +910,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0310108610197778158303030205558515510555556451055555</v>
+        <v>0310108610197778158303030205558515510555556451055555101510101562515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-6-27.xlsx
@@ -912,6 +912,9 @@
       <c r="G2" t="str">
         <v>0310108610197778158303030205558515510555556451055555101510101562515</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
